--- a/docs/Defect_Log.xlsx
+++ b/docs/Defect_Log.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2684,6 +2684,165 @@
       <c r="O28" s="4" t="inlineStr">
         <is>
           <t>2026-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="100.8" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>DEF-028</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>First-Time Setup created the database before Get Started, so abandoning setup left a half-configured system</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>First-Time Setup</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>User Acceptance Testing</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>UAT Round 2</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>BtnCustomizeFields_Click calls DatabaseManager.InitializeDatabase() so CustomizeSlipsForm can load the field list. That write committed the database before the operator had finished. Program.cs decides whether to show setup purely on whether the file exists, so closing the setup screen after using Customize Fields left a database holding seeded defaults -- the Small240x102 profile, the default company name, and none of the operator's selections -- and every later launch skipped setup entirely, with no route back to it short of deleting the file by hand.</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>1. Delete WeighbridgeData.db so First-Time Setup appears
+2. Click 'Customize Fields...' and close that window
+3. Close the setup screen with the X, WITHOUT clicking Get Started
+4. Relaunch the application</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Only Get Started commits a setup. Abandoning the screen leaves no database behind, and the next launch shows First-Time Setup again.</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>The next launch opened straight onto the Main Page against a database the operator never completed -- wrong paper size, wrong company name, and no way to re-run setup</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>FirstTimeSetupForm now tracks whether it created the database and deletes it again in OnFormClosing when the dialog result is anything other than OK. Added DatabaseManager.DeleteDatabaseFile(), which clears the SQLite connection pool first so the handle is released before the delete. Verified 2026-08-08: after Customize Fields and an X-close, the relaunch showed setup again. Referenced TC-046.</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="100.8" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>DEF-029</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Slip Length accepted letters; invalid input was only rejected on Get Started</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>First-Time Setup</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>User Acceptance Testing</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>UAT Round 2</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>The Slip Length textbox applied no input filtering, so any text could be typed into a field that only ever holds a measurement in inches. The value was validated on Get Started, but during testing the tester could not tell whether the entry had actually been blocked -- the rejection was not evident at the point of entry, unlike the Tons field which filters keystrokes as they are typed.</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>1. Open First-Time Setup
+2. Set Paper Size to Small240x102 so the Slip Length field appears
+3. Type 'abc' into Slip Length</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Letters cannot be entered at all, consistent with the Tons field. Blank or incomplete values are still caught by the Get Started validation as a backstop.</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Letters could be typed freely, and whether they had been rejected was not apparent from the screen</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>Added a KeyPress filter to Slip Length allowing digits and at most one decimal separator, plus MaxLength 6, mirroring txtField7_KeyPress on CreateSlip. The Get Started validation is retained for blank or pasted values. Verified 2026-08-08: 'abc' produced no input, '5.5' was accepted, a second separator was refused. TC-003 rewritten to assert prevention rather than a message.</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2887,7 @@
         </is>
       </c>
       <c r="D5" s="13" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -2738,7 +2897,7 @@
         </is>
       </c>
       <c r="D6" s="13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -2778,7 +2937,7 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -2798,7 +2957,7 @@
         </is>
       </c>
       <c r="D13" s="13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -2828,7 +2987,7 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">

--- a/docs/Defect_Log.xlsx
+++ b/docs/Defect_Log.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2845,6 +2845,82 @@
           <t>2026-08-08</t>
         </is>
       </c>
+    </row>
+    <row r="31" ht="100.8" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>DEF-030</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Renaming a field does not move its lookup list, and there is no way to reassign one</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Customize Slips</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>User Acceptance Testing</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>UAT Round 2</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>FieldConfig.LookupTable is assigned per field slot when the database is first created and is never changed again. Customize Slips lets the operator rename a field but offers no way to change which lookup list feeds that field's dropdown, so after a rename the field suggests values from the wrong domain. The effect compounds: SaveLookupValue writes any newly typed value into whichever table the slot is bound to, so continued use progressively mixes unrelated values into both lists.</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>1. Open Customize Slips and rename Field6 from 'Destination' to 'Slot number'
+2. Rename Field9 from 'Slot' to 'Destination'
+3. Save
+4. Open Create Slip and drop down each of those two fields</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>A field's dropdown suggests values appropriate to its current label, or the operator has some way to reassign which lookup list feeds it.</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>Field6, labelled 'Slot number', suggested destination names from the Destinations table, while Field9, labelled 'Destination', suggested slot codes from the Slots table. Any new value typed into either was saved back into the mismatched table.</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>Deferred by decision on 2026-08-10, to be addressed later. Recommended fix: expose LookupTable as an editable column in the Customize Slips Field Setup grid so the binding can be reassigned, or move the binding so it follows the label. Note that historical slips are unaffected either way: a slip stores the plain text value and never references a lookup row, per Technical Specification Section 3.1.</t>
+        </is>
+      </c>
+      <c r="M31" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="O31" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2887,7 +2963,7 @@
         </is>
       </c>
       <c r="D5" s="13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -2907,7 +2983,7 @@
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2947,7 +3023,7 @@
         </is>
       </c>
       <c r="D12" s="13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -2987,7 +3063,7 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">

--- a/docs/Defect_Log.xlsx
+++ b/docs/Defect_Log.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2921,6 +2921,165 @@
         </is>
       </c>
       <c r="O31" s="4"/>
+    </row>
+    <row r="32" ht="100.8" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEF-031</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Main Page tiles kept their old headings after a field was renamed</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Main Page</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User Acceptance Testing</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAT Round 3</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BuildTileText resolves each tile heading from FieldConfig every time it runs, so a tile built after a rename is always correct. The problem was that nothing rebuilt the existing tiles: btnCustomizeSlips_Click opened Customize Slips and did nothing with the result, so the dashboard on screen kept the headings it was drawn with. Opening Tile Display and re-saving the same selection did force a redraw, which is why re-picking the field looked like the cure -- it was rebuilding the tiles, not repairing any stored caption.</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. On the Main Page open Tile Display, choose a field such as Field10 and Save
+2. Confirm the tiles show that field's current heading
+3. Open Customize Slips, rename that field and Save
+4. Return to the Main Page without touching Tile Display</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The tiles carry the new heading as soon as the rename is saved, with no second step</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The tiles kept the previous heading. The operator had to reopen Tile Display and re-select the same field before the dashboard caught up.</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">btnCustomizeSlips_Click now reloads the dashboard, the empty state and the daily summary when Customize Slips closes with DialogResult.OK, and the Tile Display button already did the same. Verified 2026-08-11: renaming Field10 from 'Compony' to 'Client' left the tiles reading 'Client: RGN-ORE' with no further action. Referenced TC-047.</t>
+        </is>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-11</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="100.8" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEF-032</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renaming a field gave no warning of how far the change reached</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customize Slips</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User Acceptance Testing</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAT Round 3</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customize Slips committed a new label silently. A field label is used by the Create Slip form, the Slip History grid and its filter dropdowns, the View and Edit tabs, the printed slip, the Excel export headings, the Main Page tiles, the daily summary breakdown and the Manage Lookups selector -- so a rename has a reach the operator could not see before committing to it. Two consequences are especially easy to get wrong: already-recorded slips do not change, because a slip stores the value rather than the label; and the lookup list feeding that field's dropdown does not follow the rename, which is the open DEF-030 behaviour.</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open Customize Slips from the Main Page
+2. Change the label of any field
+3. Click Save</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Before the rename is committed the operator is shown exactly which labels are changing and everywhere the new wording will appear, with the option to cancel</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The rename was written straight to FieldConfig with no summary and no confirmation step</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CustomizeSlipsForm.btnSave_Click now builds a 'Renaming Fields' confirmation listing each changed label as old to new, enumerating every surface the new wording will appear on, and stating that recorded slips are unaffected and that dropdown suggestions do not follow the rename. OK commits, Cancel abandons. Verified 2026-08-11 on Field10: 'Compony' to 'Client'. Referenced TC-048.</t>
+        </is>
+      </c>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-11</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-11</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2963,7 +3122,7 @@
         </is>
       </c>
       <c r="D5" s="13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -2973,7 +3132,7 @@
         </is>
       </c>
       <c r="D6" s="13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -3023,7 +3182,7 @@
         </is>
       </c>
       <c r="D12" s="13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -3033,7 +3192,7 @@
         </is>
       </c>
       <c r="D13" s="13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -3063,7 +3222,7 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">

--- a/docs/Defect_Log.xlsx
+++ b/docs/Defect_Log.xlsx
@@ -2907,12 +2907,12 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>Deferred by decision on 2026-08-10, to be addressed later. Recommended fix: expose LookupTable as an editable column in the Customize Slips Field Setup grid so the binding can be reassigned, or move the binding so it follows the label. Note that historical slips are unaffected either way: a slip stores the plain text value and never references a lookup row, per Technical Specification Section 3.1.</t>
-        </is>
-      </c>
-      <c r="M31" s="9" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t xml:space="preserve">Suggestion lists no longer belong to a field slot. The nine fixed tables and FieldConfig.LookupTable are gone, replaced by LookupLists / LookupEntries keyed on the field's label, matched case-insensitively and ignoring a trailing colon. A list is created the first time a value is saved under a label, so a rename to an unused name starts empty and a rename back to a previous name restores that list intact. Values are captured when the slip is written rather than on leaving the box, so an abandoned form no longer feeds the list. Manage Lookups now lists every list including ones no field points at, and can clear or delete them. Existing lookup values are dropped on upgrade by decision of the project owner, since the lists rebuild from use. Side effect: the list name is now a bound parameter rather than an interpolated table name, so the lookup queries are no longer built by string concatenation. Referenced TC-049 to TC-052.</t>
+        </is>
+      </c>
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed (pending re-verification)</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -2920,7 +2920,11 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="O31" s="4"/>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-11</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="100.8" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
@@ -3132,7 +3136,7 @@
         </is>
       </c>
       <c r="D6" s="13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -3142,7 +3146,7 @@
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">

--- a/docs/Defect_Log.xlsx
+++ b/docs/Defect_Log.xlsx
@@ -2912,7 +2912,7 @@
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed (pending re-verification)</t>
+          <t xml:space="preserve">Fixed</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">

--- a/docs/Defect_Log.xlsx
+++ b/docs/Defect_Log.xlsx
@@ -2194,12 +2194,12 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>Not yet implemented in code -- recommend a cleanup in MigrateSchemaIfNeeded deleting these three superseded keys. NOTE 2026-08-07: the test database was cleared and rebuilt from scratch, and a fresh database does not contain these keys at all, so this defect does not affect the deployment. It remains open only for databases created before the 3 July refactor.</t>
-        </is>
-      </c>
-      <c r="M22" s="9" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t xml:space="preserve">Fixed 2026-08-11. A DELETE for the three superseded keys now sits in MigrateSchemaIfNeeded directly beneath the ALTER statements that added the replacement columns, which is where the 3 July migration should have put it. The keys are named explicitly rather than swept by a whitelist of live settings: an unrecognised key is far likelier to be one added after this code was written than one this refactor stranded, and deleting that would be the worse mistake. An audit of every GetGlobalSetting and SaveGlobalSetting call site confirmed these three were the only orphans; the other nine keys are all read or written by current code. Verified in a running build against the archived 7 August database, which held SlipFontScale 2.75, SlipOffsetXMm 0 and SlipOffsetYMm -1.5 against a live profile of 1.95, -1 and 0: after launch the three rows are gone, Print Calibration still reads 1.95, -1.0 and 0.0, and all 16 slips, 16 bill numbers, 3 printer profiles and 10 field labels are unchanged. Referenced TC-053.</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2207,7 +2207,11 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="O22" s="4" t="n"/>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-11</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="100.8" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
@@ -3136,7 +3140,7 @@
         </is>
       </c>
       <c r="D6" s="13" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -3146,7 +3150,7 @@
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">

--- a/docs/Defect_Log.xlsx
+++ b/docs/Defect_Log.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3086,6 +3086,402 @@
       <c r="O33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="100.8" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEF-033</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Copies on one page were locked to a single arrangement</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Printing</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer Acceptance Testing</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer Testing Round 1</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RenderSlipForPreview decided the arrangement itself: two copies always as two columns split by a vertical cut line, four always as a 2x2 grid. Which way the copies sit decides which way the page is torn or guillotined, and that follows from the customer's paper and how they handle it rather than from anything the software can know. No setting exposed the choice.</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open Printer Settings and click Calibration Page
+2. Set Copies to 2
+3. Look at the preview, then click Print Test Page
+4. Repeat with Copies set to 4</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The operator chooses whether copies sit side by side or stacked, and the printed sheet matches the preview exactly</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two copies always printed side by side and four always as a 2x2 grid. There was no way to change it.</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added an Arrangement setting beside Copies offering Side by side, Stacked, and Grid (2 x 2), the last only when 4 copies is selected since for two it would behave as side by side. Stored per preset in a new PrinterProfiles.MultiSlipLayout column defaulting to 'Columns', so an existing preset prints exactly as it did before. The tiling decision moved into SlipPrintEngine.GetTiling, which the print path, the calibration preview and the preview's bitmap sizing all call, so the paper can never disagree with the screen. The preview bitmap is now built at the cell's real proportions, so a stacked copy is laid out wide and short rather than drawn tall and squashed. Referenced TC-054.</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed (pending re-verification)</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="100.8" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEF-034</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Printing to PDF opened a Save dialog with no file name filled in</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Printing</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer Acceptance Testing</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer Testing Round 1</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Save Print Output As dialog raised by Microsoft Print to PDF opened with an empty File name box, so the operator had to invent and type a name for every slip. PrintDocument.DocumentName was never set. Setting it alone does not fix this: it renames the print job, which is why the name appears in the Printing progress window, while the driver's own Save dialog ignores it entirely.</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Choose Microsoft Print to PDF as the printer
+2. Create a slip and click Print, then confirm the preview
+3. Look at the File name box in the Save dialog</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Save dialog opens with a sensible name already in it, still editable, so a folder of saved slips can be read at a glance</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The File name box was empty on every slip.</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The application now raises its own SaveFileDialog, pre-filled with the bill number and the leading visible field's value (for example '20260812-091335 - LFN550NW'), and hands the chosen path to the driver through PrintToFile and PrintFileName. Given a path the driver writes straight to it and does not prompt again, so the operator still sees exactly one dialog. The leading field follows the operator's own field order rather than being fixed to Field1, characters Windows rejects in a file name are stripped, and the folder last saved into is remembered. Verified 2026-08-13. Referenced TC-055.</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="100.8" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEF-035</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cancelling the PDF Save dialog marked the slip Printed with no document produced</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slip Lifecycle</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Critical</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Critical</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Code Review</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer Testing Round 1</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PrintDocument.Print() returns normally when the operator cancels the printer driver's own Save dialog - the driver discards the job rather than raising an error. PrintSlipPreview.BtnPrint_Click set DialogResult.OK as soon as Print() returned, and CreateSlip marks the slip Printed on that result. Cancelling therefore recorded a printed slip with no document anywhere, and a printed slip can never be un-printed. Found while fixing DEF-034. It can only occur on the print-to-file path, which is why 53 passing test cases had never reached it.</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Choose Microsoft Print to PDF as the printer
+2. Create a slip and click Print, then confirm the preview
+3. Click Cancel on the Save dialog
+4. Find the slip in Slip History and check its status</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A cancelled print leaves the slip an unprinted draft on the Main Page, since nothing was produced</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The slip was marked Printed although no PDF was written, and being printed it could then only be voided, never returned to draft</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Save dialog is now the application's own, and its result is checked before anything is printed. Cancelling returns without printing and without setting DialogResult.OK, so the slip stays a draft. Referenced TC-056.</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed (pending re-verification)</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="100.8" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEF-036</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The company logo was stored as a file path, so it could not travel with the system</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Printing</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Code Review</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer Testing Round 1</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GlobalSettings.LogoPath held an absolute path to a picture elsewhere on the machine. Handing the application to anyone else broke it immediately since that path does not exist on their PC, and the customer moving or deleting their own file broke it just as easily. The draw was guarded by File.Exists and wrapped in an empty catch, so a missing or unreadable picture printed a slip with no letterhead and reported nothing at all.</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Set a logo from a file in Customize Slips
+2. Move, rename or delete that file - or copy the application to another machine
+3. Print a slip</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A configured logo prints wherever the application runs and whatever happens to the original file, and a logo that cannot be loaded is reported rather than silently dropped</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The slip printed with no logo and no message. Nothing indicated the letterhead was missing.</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The image is stored in the database, so it travels with the file, is captured by every backup, and cannot be broken by moving or deleting anything. A stored logo that will not decode now reports the failure instead of quietly omitting the letterhead. The old LogoPath is read once during migration and the picture pulled in if it still resolves, so a logo configured before this change survives the upgrade rather than being lost. Verified 2026-08-13. Referenced TC-057.</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="100.8" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEF-037</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Company Name and Slip Length boxes overlapped on the Printer Settings screen</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Printer Settings</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User Acceptance Testing</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer Testing Round 1</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The two right-column rows were positioned 15px apart while the text boxes are 22px tall, so they overlapped by 7px and rendered as one tall control holding two lines of text. The margin rows below already used a 38px pitch; only this pair was wrong. Both boxes also ran past the form's right edge once Windows scaled the form up on a high-DPI display, since the form is AutoScaleMode.Font and a control that clears the edge at design size need not clear it once scaled.</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open Printer Settings
+2. Look at the Company Name and Slip Length fields</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Each field has its own clearly separated box, and both sit well inside the form at any display scaling</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The two boxes overlapped and read as a single control with two lines of text in it, and both ran to the form's right edge</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The right column now uses one running row pitch matching the margins below it, so the pair cannot drift into each other again and a row added later needs no hand-adjusted coordinates. Control width dropped from 230 to 190 and the form's client width went from 950 to 1020. Verified 2026-08-13. Referenced TC-058.</t>
+        </is>
+      </c>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3526,7 @@
         </is>
       </c>
       <c r="D5" s="13" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
@@ -3140,7 +3536,7 @@
         </is>
       </c>
       <c r="D6" s="13" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -3170,7 +3566,7 @@
         </is>
       </c>
       <c r="D10" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -3180,7 +3576,7 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -3200,7 +3596,7 @@
         </is>
       </c>
       <c r="D13" s="13" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -3220,7 +3616,7 @@
         </is>
       </c>
       <c r="D16" s="13" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -3230,13 +3626,23 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Customer Acceptance Testing (review)</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>Note: 'Code Review' = defects found through static analysis of source code against the project specification, before runtime testing. 'User Acceptance Testing' = defects found through hands-on, exploratory use of the running application by an end-stage tester.</t>
+          <t xml:space="preserve">Note: 'Code Review' = defects found through static analysis of source code against the project specification, before runtime testing. 'User Acceptance Testing' = defects found through hands-on, exploratory use of the running application by an end-stage tester. 'Customer Acceptance Testing' = defects raised by the customer while reviewing a pre-release build. All three are pre-deployment: the system has not been used in live operation, and no defect in this log was found during operational use.</t>
         </is>
       </c>
     </row>

--- a/docs/Defect_Log.xlsx
+++ b/docs/Defect_Log.xlsx
@@ -3309,12 +3309,12 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Save dialog is now the application's own, and its result is checked before anything is printed. Cancelling returns without printing and without setting DialogResult.OK, so the slip stays a draft. Referenced TC-056.</t>
+          <t xml:space="preserve">The Save dialog is now the application's own, and its result is checked before anything is printed. Cancelling returns without printing and without setting DialogResult.OK, so the slip stays a draft. Verified 2026-08-17: cancelling the Save dialog left the slip's tile on the Main Page and it did not appear among the printed slips. Referenced TC-056.</t>
         </is>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed (pending re-verification)</t>
+          <t xml:space="preserve">Fixed</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-13</t>
+          <t xml:space="preserve">2026-08-17</t>
         </is>
       </c>
     </row>

--- a/docs/Defect_Log.xlsx
+++ b/docs/Defect_Log.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed (pending re-verification)</t>
+          <t xml:space="preserve">Fixed</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -3482,6 +3482,86 @@
       <c r="O38" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="100.8" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEF-038</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Landscape rotated the paper but not the layout, so the lower part of the page printed off the sheet</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Printing</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User Acceptance Testing</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer Testing Round 1</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PageSettings.Landscape was set, so the driver duly turned an A4 sheet to 297 x 210. The renderer, however, kept laying content out for the profile's stored 210 x 297. It therefore arranged a 190 x 277 mm column of content and sent it to a sheet only 190 mm tall. Everything below that line fell off the paper. With two copies on a page the first slip printed and the second ran off the bottom. The same disagreement reached both preview canvases, which drew a portrait page while the printer produced a landscape one.</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Printer Settings: set Orientation to Landscape on the active preset and save
+2. Set Copies per page to 2 on the calibration screen
+3. Print a slip, to paper or to PDF
+4. Compare what came out against the preview</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The sheet prints landscape and the content is laid out for the landscape shape, with both previews showing the same page the printer produces</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The page rotated but the content did not: the first slip printed and the second was cut off by the bottom edge of the sheet. Both previews showed a portrait page throughout.</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Split the two ideas of the page apart. GetPaperStockMm returns the stock's own unrotated size and is what the driver's PaperSize receives, alongside the Landscape flag that actually performs the rotation. GetPageDimensionsMm returns that swapped, and is what everything that draws uses -- the renderer, both preview canvases and the multi-copy cell maths. Also corrected an interim attempt that expressed landscape purely as a swapped PaperSize with no rotation flag: the driver ignores a custom size on its own and silently prints portrait, so the previews turned landscape while the paper did not. Verified 2026-08-17 against PDF output in both orientations. Referenced TC-059.</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-17</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-17</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3606,7 @@
         </is>
       </c>
       <c r="D5" s="13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
@@ -3536,7 +3616,7 @@
         </is>
       </c>
       <c r="D6" s="13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -3576,7 +3656,7 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -3626,7 +3706,7 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">

--- a/docs/Defect_Log.xlsx
+++ b/docs/Defect_Log.xlsx
@@ -1240,12 +1240,12 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>Dialog layout corrected so prompt text sits fully visible above the textbox with proper spacing</t>
+          <t xml:space="preserve">Dialog layout corrected so prompt text sits fully visible above the textbox with proper spacing Re-verified 2026-08-08 by TC-019, TC-020 and TC-021, which exercised the void reason prompt on both an unprinted draft and a printed slip.</t>
         </is>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>Fixed (pending re-verification)</t>
+          <t xml:space="preserve">Fixed</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>Added an instruction label describing how to use the grid; Field1/Field7 Hidden and Required checkboxes now visibly disabled with a note explaining these two fields are always required and always visible</t>
+          <t xml:space="preserve">Added an instruction label describing how to use the grid; Field1/Field7 Hidden and Required checkboxes now visibly disabled with a note explaining these two fields are always required and always visible Re-verified 2026-08-10 by TC-023, TC-024 and TC-025, which exercised the label cap and the locked Truck Reg and Tons fields on the Customize Slips screen.</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>Fixed (pending re-verification)</t>
+          <t xml:space="preserve">Fixed</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">

--- a/docs/Defect_Log.xlsx
+++ b/docs/Defect_Log.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3562,6 +3562,164 @@
       <c r="O39" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="100.8" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEF-039</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Backups could not be restored from inside the application</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Backup</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Code Review</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Review Round 6</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PerformStartupBackup and PerformManualBackup wrote copies; nothing ever read one back. The word 'restore' did not appear anywhere in the codebase. Recovering from a damaged database meant closing the program, finding %ProgramData%\UitvalSlips by hand, renaming files, and knowing to delete stray -journal files first. On a system whose purpose is holding the permanent record of what left the yard, a backup the operator cannot actually use is half a feature, and the missing half is the one needed on a bad morning.</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Note that copies exist in the Backups folder
+2. Open the application and look for any way to put one back
+3. Search the source for a restore path</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The operator can choose a backup and put it back from inside the program, without file surgery and without telephoning the developer.</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No restore existed. The only route was manual file manipulation in a hidden system folder.</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added a Restore screen listing every backup with its age and the slip counts read from the file itself, so the operator can see what each copy holds before choosing. A copy that will not open is shown in red and cannot be selected. The restore validates the chosen backup before touching anything, moves the current database aside as WeighbridgeData_replaced_&lt;timestamp&gt;.db rather than deleting it, puts the original back if the copy fails, clears pooled SQLite handles so the file is not locked, and removes stray -journal and -wal files belonging to the replaced database which SQLite would otherwise try to apply to the restored one. Referenced TC-060 and TC-061.</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-18</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="100.8" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEF-040</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automatic backups were taken only at launch, so a fault mid-day cost the whole day</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Backup</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Code Review</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Review Round 6</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PerformStartupBackup was called once from Program.Main and was the only automatic backup in the system. An operator starting at 06:00 and working until 16:00 therefore had exactly one copy, taken at 06:00. Any database fault during the day rolled the records back ten hours, and every slip issued in between would have existed only on paper.</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Start the application
+2. Enter and print several slips over the course of a day
+3. Inspect the Backups folder for any copy taken after startup</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Backups follow the work being done, so a database fault costs minutes rather than a day.</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One backup per launch, and nothing after it however many slips were entered.</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Backups now follow each committed change -- a draft saved, a slip printed, edited or voided -- throttled to at most one every fifteen minutes so a busy morning does not fill the disk with near-identical copies. Startup still forces one regardless of the interval. Retention changed to match: every copy from the last three days, then the first copy of each day out to thirty, since the previous flat thirty-day rule combined with quarter-hourly backups would have left several hundred files. Referenced TC-062.</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-18</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-18</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3764,7 @@
         </is>
       </c>
       <c r="D5" s="13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -3616,7 +3774,7 @@
         </is>
       </c>
       <c r="D6" s="13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -3656,7 +3814,7 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -3696,7 +3854,7 @@
         </is>
       </c>
       <c r="D16" s="13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">

--- a/docs/Defect_Log.xlsx
+++ b/docs/Defect_Log.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3720,6 +3720,86 @@
       <c r="O41" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="100.8" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEF-041</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The licence check refused the very computer its licence was issued for</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licensing</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Critical</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Critical</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User Acceptance Testing</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAT Round 4</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MachineFingerprint.Components returns the full 64-character SHA-256 of each of the three hardware identifiers. A machine code carries only the first ten characters of each, which is therefore all ParseMachineCode can hand back. Compare tested the full sixty-four against those ten and so could never report a match on any machine, under any circumstances. The signature check was sound, so a licence verified as genuine and was then rejected as belonging to a different computer -- while the screen displayed the licensed code and the machine code as identical strings.</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Read the machine code from the licence screen
+2. Issue a licence for exactly that code
+3. Paste it in and click Activate
+4. Compare the two codes shown in the refusal message</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A licence issued for this computer activates on this computer.</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Refused with 'genuine but issued for a different computer', quoting a licensed code and a machine code that were character-for-character the same. Every install would have failed this way on first use.</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Both sides now truncate through a single Prefix helper, so the ten-character length is defined once rather than being set in MachineCode and separately assumed in Compare. Verified 2026-08-19 on the machine that had just refused itself. Referenced TC-063.</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
     </row>
@@ -3764,7 +3844,7 @@
         </is>
       </c>
       <c r="D5" s="13" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
@@ -3774,7 +3854,7 @@
         </is>
       </c>
       <c r="D6" s="13" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -3804,7 +3884,7 @@
         </is>
       </c>
       <c r="D10" s="13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -3864,7 +3944,7 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">

--- a/docs/Defect_Log.xlsx
+++ b/docs/Defect_Log.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3798,6 +3798,86 @@
         </is>
       </c>
       <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="100.8" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEF-042</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Printer Settings wrote stale margins back over the calibration just measured</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Printer Settings</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User Acceptance Testing</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAT Round 5</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The calibration screen writes paper size and margins to the same PrinterProfiles columns the Printer Settings form edits. btnCalibration_Click opened the dialog and did nothing on its return, so the parent's spinners still held the values loaded before calibrating. The next Save Configuration wrote those back over the measurements. Calibration saved correctly and was undone one step later, so the reported symptom was that calibration did not save at all while the stored row showed that it had. Two further faults sat alongside it. The two entry points resolved the target profile by different rules -- by ProfileName when opened from Printer Settings, by IsActive when opened from the print preview -- which coincide with a single profile but would edit different rows once several presets exist, with nothing on screen naming which. And saving with no active profile reported 'Calibration settings saved to (no active profile)' while writing nothing.</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open Printer Settings and note the Right margin
+2. Click Calibration Page, change Right, click Save Settings
+3. Back in Printer Settings click Save Configuration
+4. Reopen Printer Settings and read the Right margin</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A margin measured during calibration survives, and both calibration routes always read and write the preset chosen in Printer Settings.</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The calibrated margin was replaced by the value Printer Settings had been displaying since before calibration. Found while calibrating a real slip against the EPSON LX-350: the printed output kept reverting to the uncalibrated layout even though the calibration screen had reported saving.</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Printer Settings now reloads from the database when the calibration dialog closes, so it can no longer write stale values over it. A single ResolveTarget, always the active profile, serves both load and save, and Printer Settings activates the selected preset before opening calibration, so the two routes cannot address different rows. The window title names the profile being written to, identically from both routes. Saving with no active profile now refuses and says where to go instead. Verified 2026-08-19 against the stored row and on paper on the LX-350. Referenced TC-066 and TC-067.</t>
+        </is>
+      </c>
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
@@ -3844,7 +3924,7 @@
         </is>
       </c>
       <c r="D5" s="13" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -3854,7 +3934,7 @@
         </is>
       </c>
       <c r="D6" s="13" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -3894,7 +3974,7 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -3944,7 +4024,7 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">

--- a/docs/Defect_Log.xlsx
+++ b/docs/Defect_Log.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3878,6 +3878,84 @@
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="100.8" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEF-043</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The installer and the program inside it reported different version numbers</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deployment</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Code Review</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Review Round 7</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Inno Setup script carried a hand-typed AppVersion of 1.0.0 while AssemblyInfo.cs declared 1.1.0.0, so Add/Remove Programs and the installer filename disagreed with the program's own About metadata. Nothing malfunctioned, but the question 'which version are you running?' had two answers depending on where it was asked -- and that question is asked precisely when something has already gone wrong and the answer needs to be trusted.</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Build the installer
+2. Compare its file properties with those of SlipManagement2.exe inside the payload</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One version number, reported identically by the installer, by Add/Remove Programs and by the program itself.</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The installer reported 1.0.0 and the program 1.1.0.0. Caught while verifying the first build, before any copy was handed over.</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AssemblyInfo.cs is now the single place a version is set, and the installer reads it back out of the built exe with GetVersionNumbersString rather than repeating it. Setting the two equal would have corrected this build and let them drift again at the next one, since the fault was two hand-maintained numbers rather than the values they held. If the payload has not been staged the compile now fails outright, which is preferable to producing a correctly built installer wearing a wrong label. Verified: UitvalSlips-Setup-1.1.0.0.exe, both reporting 1.1.0.0.</t>
+        </is>
+      </c>
+      <c r="M44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-19</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-19</t>
         </is>
@@ -3924,7 +4002,7 @@
         </is>
       </c>
       <c r="D5" s="13" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -3934,7 +4012,7 @@
         </is>
       </c>
       <c r="D6" s="13" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -3994,7 +4072,7 @@
         </is>
       </c>
       <c r="D13" s="13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
@@ -4014,7 +4092,7 @@
         </is>
       </c>
       <c r="D16" s="13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
